--- a/data/EVALUACIONES/SALTOS/SALTOS.xlsx
+++ b/data/EVALUACIONES/SALTOS/SALTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\SALTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D406DF1-0B26-4A55-8D71-A89874212824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243B7487-A61A-4395-BC78-EC885EE030A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -668,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O2" s="3">
         <v>0.87099537037037034</v>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O3" s="3">
         <v>0.87246527777777783</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O4" s="3">
         <v>0.87361111111111112</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O5" s="3">
         <v>0.87497685185185181</v>
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O6" s="3">
         <v>0.87586805555555558</v>
@@ -903,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O7" s="3">
         <v>0.87668981481481478</v>
@@ -950,7 +950,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O8" s="3">
         <v>0.87793981481481487</v>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O9" s="3">
         <v>0.87891203703703702</v>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O10" s="3">
         <v>0.86682870370370368</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O11" s="3">
         <v>0.86849537037037039</v>
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O12" s="3">
         <v>0.86954861111111115</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O13" s="3">
         <v>0.87031250000000004</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O14" s="3">
         <v>0.87124999999999997</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O15" s="3">
         <v>0.8718055555555555</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O16" s="3">
         <v>0.85290509259259262</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O17" s="3">
         <v>0.85362268518518514</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O18" s="3">
         <v>0.85415509259259259</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O19" s="3">
         <v>0.85488425925925926</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O20" s="3">
         <v>0.85574074074074069</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O21" s="3">
         <v>0.85622685185185188</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O22" s="3">
         <v>0.8568634259259259</v>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O23" s="3">
         <v>0.85738425925925921</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O24" s="3">
         <v>0.85777777777777775</v>
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O25" s="3">
         <v>0.85980324074074077</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O26" s="3">
         <v>0.86054398148148148</v>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O27" s="3">
         <v>0.86149305555555555</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O28" s="3">
         <v>0.86275462962962968</v>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O29" s="3">
         <v>0.86390046296296297</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O30" s="3">
         <v>0.86471064814814813</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O31" s="3">
         <v>0.86552083333333329</v>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O32" s="3">
         <v>0.86618055555555551</v>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O33" s="3">
         <v>0.86717592592592596</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O34" s="3">
         <v>0.87594907407407407</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O35" s="3">
         <v>0.87690972222222219</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O36" s="3">
         <v>0.87809027777777782</v>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O37" s="3">
         <v>0.87958333333333338</v>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O38" s="3">
         <v>0.88086805555555558</v>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="N39" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O39" s="3">
         <v>0.88153935185185184</v>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O40" s="3">
         <v>0.85424768518518523</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O41" s="3">
         <v>0.85518518518518516</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O42" s="3">
         <v>0.85707175925925927</v>
@@ -2595,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O43" s="3">
         <v>0.85865740740740737</v>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O44" s="3">
         <v>0.85947916666666668</v>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O45" s="3">
         <v>0.86001157407407403</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O46" s="3">
         <v>0.85467592592592589</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O47" s="3">
         <v>0.85585648148148152</v>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O48" s="3">
         <v>0.85741898148148143</v>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="N49" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O49" s="3">
         <v>0.85898148148148146</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O50" s="3">
         <v>0.85971064814814813</v>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O51" s="3">
         <v>0.86026620370370366</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="N52" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O52" s="3">
         <v>0.86008101851851848</v>
@@ -3065,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="N53" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O53" s="3">
         <v>0.86083333333333334</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="N54" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O54" s="3">
         <v>0.86175925925925922</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="N55" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O55" s="3">
         <v>0.86306712962962961</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O56" s="3">
         <v>0.86421296296296302</v>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="N57" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O57" s="3">
         <v>0.8649768518518518</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O58" s="3">
         <v>0.86572916666666666</v>
@@ -3347,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="N59" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O59" s="3">
         <v>0.86657407407407405</v>
@@ -3394,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O60" s="3">
         <v>0.86736111111111114</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O61" s="3">
         <v>0.8682523148148148</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="N62" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O62" s="3">
         <v>0.86905092592592592</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="N63" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O63" s="3">
         <v>0.87019675925925921</v>
@@ -3582,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="N64" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O64" s="3">
         <v>0.87089120370370365</v>
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="N65" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O65" s="3">
         <v>0.87167824074074074</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="N66" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O66" s="3">
         <v>0.8722685185185185</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="N67" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O67" s="3">
         <v>0.86996527777777777</v>
@@ -3770,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="N68" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O68" s="3">
         <v>0.87119212962962966</v>
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O69" s="3">
         <v>0.87277777777777776</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O70" s="3">
         <v>0.87430555555555556</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O71" s="3">
         <v>0.87512731481481476</v>
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O72" s="3">
         <v>0.87619212962962967</v>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="N73" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O73" s="3">
         <v>0.87699074074074079</v>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="N74" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O74" s="3">
         <v>0.87832175925925926</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O75" s="3">
         <v>0.84401620370370367</v>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="N76" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O76" s="3">
         <v>0.84495370370370371</v>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="N77" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O77" s="3">
         <v>0.84611111111111115</v>
@@ -4240,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="N78" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O78" s="3">
         <v>0.84696759259259258</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="N79" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O79" s="3">
         <v>0.84788194444444442</v>
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="N80" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O80" s="3">
         <v>0.84837962962962965</v>
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="N81" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O81" s="3">
         <v>0.87035879629629631</v>
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="N82" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O82" s="3">
         <v>0.87193287037037037</v>
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="N83" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O83" s="3">
         <v>0.87327546296296299</v>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="N84" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O84" s="3">
         <v>0.87442129629629628</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="N85" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O85" s="3">
         <v>0.87541666666666662</v>
@@ -4616,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="N86" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O86" s="3">
         <v>0.87633101851851847</v>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="N87" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O87" s="3">
         <v>0.87732638888888892</v>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="N88" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O88" s="3">
         <v>0.87866898148148154</v>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="N89" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O89" s="3">
         <v>0.87642361111111111</v>
@@ -4804,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="N90" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O90" s="3">
         <v>0.87725694444444446</v>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="N91" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O91" s="3">
         <v>0.87887731481481479</v>
@@ -4898,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="N92" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O92" s="3">
         <v>0.88025462962962964</v>
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="N93" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O93" s="3">
         <v>0.88061342592592595</v>
@@ -4992,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="N94" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O94" s="3">
         <v>0.88112268518518522</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="N95" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O95" s="3">
         <v>0.86038194444444449</v>
@@ -5086,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O96" s="3">
         <v>0.86106481481481478</v>
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="N97" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O97" s="3">
         <v>0.86193287037037036</v>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="N98" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O98" s="3">
         <v>0.86327546296296298</v>
@@ -5227,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O99" s="3">
         <v>0.86449074074074073</v>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="N100" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O100" s="3">
         <v>0.86535879629629631</v>
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O101" s="3">
         <v>0.86591435185185184</v>
@@ -5368,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="N102" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O102" s="3">
         <v>0.86694444444444441</v>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O103" s="3">
         <v>0.86752314814814813</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="N104" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O104" s="3">
         <v>0.87085648148148154</v>
@@ -5509,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="N105" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O105" s="3">
         <v>0.87224537037037042</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="N106" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O106" s="3">
         <v>0.87349537037037039</v>
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="N107" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O107" s="3">
         <v>0.87486111111111109</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="N108" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O108" s="3">
         <v>0.87561342592592595</v>
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="N109" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O109" s="3">
         <v>0.8765856481481481</v>
@@ -5744,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="N110" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O110" s="3">
         <v>0.87753472222222217</v>
@@ -5791,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O111" s="3">
         <v>0.87880787037037034</v>
@@ -5838,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="N112" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O112" s="3">
         <v>0.85239583333333335</v>
@@ -5885,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="N113" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O113" s="3">
         <v>0.85319444444444448</v>
@@ -5932,7 +5932,7 @@
         <v>0</v>
       </c>
       <c r="N114" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O114" s="3">
         <v>0.85381944444444446</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="N115" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O115" s="3">
         <v>0.85456018518518517</v>
@@ -6026,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="N116" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O116" s="3">
         <v>0.85510416666666667</v>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="N117" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O117" s="3">
         <v>0.8559606481481481</v>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="N118" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O118" s="3">
         <v>0.85645833333333332</v>
@@ -6167,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="N119" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O119" s="3">
         <v>0.857025462962963</v>
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="N120" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O120" s="3">
         <v>0.85754629629629631</v>
@@ -6261,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="N121" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O121" s="3">
         <v>0.84004629629629635</v>
@@ -6308,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="N122" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O122" s="3">
         <v>0.8407175925925926</v>
@@ -6355,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="N123" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O123" s="3">
         <v>0.84175925925925921</v>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="N124" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O124" s="3">
         <v>0.84275462962962966</v>
@@ -6449,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O125" s="3">
         <v>0.84359953703703705</v>
@@ -6496,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="N126" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O126" s="3">
         <v>0.84515046296296292</v>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="N127" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O127" s="3">
         <v>0.84589120370370374</v>
@@ -6590,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="N128" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O128" s="3">
         <v>0.86697916666666663</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="N129" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O129" s="3">
         <v>0.8686342592592593</v>
@@ -6684,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="N130" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O130" s="3">
         <v>0.86980324074074078</v>
@@ -6731,7 +6731,7 @@
         <v>0</v>
       </c>
       <c r="N131" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O131" s="3">
         <v>0.87047453703703703</v>
@@ -6778,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="N132" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O132" s="3">
         <v>0.87138888888888888</v>
@@ -6825,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="N133" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O133" s="3">
         <v>0.8719675925925926</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O134" s="3">
         <v>0.85276620370370371</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="N135" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O135" s="3">
         <v>0.85340277777777773</v>
@@ -6966,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="N136" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O136" s="3">
         <v>0.85398148148148145</v>
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
       <c r="N137" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O137" s="3">
         <v>0.85473379629629631</v>
@@ -7060,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="N138" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O138" s="3">
         <v>0.85523148148148154</v>
@@ -7107,7 +7107,7 @@
         <v>0</v>
       </c>
       <c r="N139" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O139" s="3">
         <v>0.85609953703703701</v>
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="N140" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O140" s="3">
         <v>0.8566435185185185</v>
@@ -7201,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="N141" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O141" s="3">
         <v>0.85726851851851849</v>
@@ -7248,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="N142" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O142" s="3">
         <v>0.85765046296296299</v>
@@ -7295,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="N143" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O143" s="3">
         <v>0.87616898148148148</v>
@@ -7342,7 +7342,7 @@
         <v>0</v>
       </c>
       <c r="N144" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O144" s="3">
         <v>0.87703703703703706</v>
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="N145" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O145" s="3">
         <v>0.8783333333333333</v>
@@ -7436,7 +7436,7 @@
         <v>0</v>
       </c>
       <c r="N146" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O146" s="3">
         <v>0.88009259259259254</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="N147" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O147" s="3">
         <v>0.8810069444444445</v>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
       <c r="N148" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O148" s="3">
         <v>0.88170138888888894</v>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="N149" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O149" s="3">
         <v>0.83969907407407407</v>
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="N150" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O150" s="3">
         <v>0.8405555555555555</v>
@@ -7671,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O151" s="3">
         <v>0.84163194444444445</v>
@@ -7718,7 +7718,7 @@
         <v>0</v>
       </c>
       <c r="N152" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O152" s="3">
         <v>0.84261574074074075</v>
@@ -7765,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="N153" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O153" s="3">
         <v>0.84341435185185187</v>
@@ -7812,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="N154" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O154" s="3">
         <v>0.8449768518518519</v>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="N155" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O155" s="3">
         <v>0.84572916666666664</v>
@@ -7906,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="N156" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O156" s="3">
         <v>0.86763888888888885</v>
@@ -7953,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="N157" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O157" s="3">
         <v>0.86883101851851852</v>
@@ -8000,7 +8000,7 @@
         <v>0</v>
       </c>
       <c r="N158" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O158" s="3">
         <v>0.87002314814814818</v>
@@ -8047,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="N159" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O159" s="3">
         <v>0.87063657407407402</v>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="N160" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O160" s="3">
         <v>0.87153935185185183</v>
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="N161" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O161" s="3">
         <v>0.87212962962962959</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="N162" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O162" s="3">
         <v>0.85443287037037041</v>
@@ -8235,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="N163" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O163" s="3">
         <v>0.85556712962962966</v>
@@ -8282,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="N164" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O164" s="3">
         <v>0.85723379629629626</v>
@@ -8329,7 +8329,7 @@
         <v>0</v>
       </c>
       <c r="N165" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O165" s="3">
         <v>0.85883101851851851</v>
@@ -8376,7 +8376,7 @@
         <v>0</v>
       </c>
       <c r="N166" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O166" s="3">
         <v>0.8595949074074074</v>
@@ -8423,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="N167" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O167" s="3">
         <v>0.86016203703703709</v>
@@ -8470,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="N168" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O168" s="3">
         <v>0.84378472222222223</v>
@@ -8517,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="N169" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O169" s="3">
         <v>0.84478009259259257</v>
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="N170" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O170" s="3">
         <v>0.84591435185185182</v>
@@ -8611,7 +8611,7 @@
         <v>0</v>
       </c>
       <c r="N171" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O171" s="3">
         <v>0.84672453703703698</v>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="N172" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O172" s="3">
         <v>0.84755787037037034</v>
@@ -8705,7 +8705,7 @@
         <v>0</v>
       </c>
       <c r="N173" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O173" s="3">
         <v>0.8482291666666667</v>
@@ -8752,7 +8752,7 @@
         <v>0</v>
       </c>
       <c r="N174" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O174" s="3">
         <v>0.84442129629629625</v>
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="N175" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O175" s="3">
         <v>0.84540509259259256</v>
@@ -8846,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="N176" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O176" s="3">
         <v>0.84630787037037036</v>
@@ -8893,7 +8893,7 @@
         <v>0</v>
       </c>
       <c r="N177" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O177" s="3">
         <v>0.84733796296296293</v>
@@ -8940,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="N178" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O178" s="3">
         <v>0.8480671296296296</v>
@@ -8987,7 +8987,7 @@
         <v>0</v>
       </c>
       <c r="N179" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O179" s="3">
         <v>0.84864583333333332</v>
@@ -9034,7 +9034,7 @@
         <v>0</v>
       </c>
       <c r="N180" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O180" s="3">
         <v>0.85502314814814817</v>
@@ -9081,7 +9081,7 @@
         <v>0</v>
       </c>
       <c r="N181" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O181" s="3">
         <v>0.8539930555555556</v>
@@ -9128,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="N182" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O182" s="3">
         <v>0.85682870370370368</v>
@@ -9175,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="N183" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O183" s="3">
         <v>0.85851851851851857</v>
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="N184" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O184" s="3">
         <v>0.85935185185185181</v>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="N185" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="O185" s="3">
         <v>0.85987268518518523</v>
@@ -9316,7 +9316,7 @@
         <v>0</v>
       </c>
       <c r="N186" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O186" s="3">
         <v>0.83939814814814817</v>
@@ -9363,7 +9363,7 @@
         <v>0</v>
       </c>
       <c r="N187" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O187" s="3">
         <v>0.8404166666666667</v>
@@ -9410,7 +9410,7 @@
         <v>0</v>
       </c>
       <c r="N188" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O188" s="3">
         <v>0.84149305555555554</v>
@@ -9457,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="N189" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O189" s="3">
         <v>0.84244212962962961</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="N190" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O190" s="3">
         <v>0.84321759259259255</v>
@@ -9551,7 +9551,7 @@
         <v>0</v>
       </c>
       <c r="N191" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O191" s="3">
         <v>0.8443518518518518</v>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
       <c r="N192" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O192" s="3">
         <v>0.84560185185185188</v>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="N193" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O193" s="3">
         <v>0.84018518518518515</v>
@@ -9692,7 +9692,7 @@
         <v>0</v>
       </c>
       <c r="N194" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O194" s="3">
         <v>0.84107638888888892</v>
@@ -9739,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="N195" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O195" s="3">
         <v>0.84189814814814812</v>
@@ -9786,7 +9786,7 @@
         <v>0</v>
       </c>
       <c r="N196" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O196" s="3">
         <v>0.84288194444444442</v>
@@ -9833,7 +9833,7 @@
         <v>0</v>
       </c>
       <c r="N197" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O197" s="3">
         <v>0.84378472222222223</v>
@@ -9880,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="N198" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O198" s="3">
         <v>0.84541666666666671</v>
@@ -9927,7 +9927,7 @@
         <v>0</v>
       </c>
       <c r="N199" s="2">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O199" s="3">
         <v>0.84620370370370368</v>

--- a/data/EVALUACIONES/SALTOS/SALTOS.xlsx
+++ b/data/EVALUACIONES/SALTOS/SALTOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\SALTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243B7487-A61A-4395-BC78-EC885EE030A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BE7A00-79D9-456D-A745-A053E3BDD699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -223,13 +223,13 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -248,7 +248,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AEC1F9C7-B230-4260-879C-528A4474077A}" name="Tabla1" displayName="Tabla1" ref="A1:P199" totalsRowShown="0">
   <autoFilter ref="A1:P199" xr:uid="{AEC1F9C7-B230-4260-879C-528A4474077A}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{4BA730B7-AA1C-42F2-810B-84C2DD5A4C89}" name="Nombre de atleta" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{4BA730B7-AA1C-42F2-810B-84C2DD5A4C89}" name="Nombre de atleta" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{495E4E94-11B3-43E5-ADB9-7D34A29B6091}" name="ID de salto"/>
     <tableColumn id="3" xr3:uid="{BF9032F0-6CCE-4FB6-A2C3-3C4A09D220EA}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{FF2A5709-4220-4467-B002-B7857FD2EA73}" name="TC"/>
@@ -261,8 +261,8 @@
     <tableColumn id="11" xr3:uid="{96E7B070-2983-48C8-98D5-E5700599E42F}" name="Rigidez"/>
     <tableColumn id="12" xr3:uid="{8C258C0D-795E-44D4-AC53-688CA4AE0D00}" name="Velocidad inicial"/>
     <tableColumn id="13" xr3:uid="{66029D8C-02BB-468B-8793-A94CE40D530E}" name="RSI"/>
-    <tableColumn id="14" xr3:uid="{847C353E-4493-4EA7-9AF0-AB72ED266170}" name="Fecha y hora" dataDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{E4D8B504-2B0D-4F13-B89C-C4B21905A819}" name="DescripciÃ³n" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{847C353E-4493-4EA7-9AF0-AB72ED266170}" name="Fecha y hora" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{E4D8B504-2B0D-4F13-B89C-C4B21905A819}" name="DescripciÃ³n" dataDxfId="1"/>
     <tableColumn id="16" xr3:uid="{D57FE126-347C-42BD-AC9F-87A4942E87E8}" name="Simulado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7866,7 +7866,7 @@
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A156" s="1" t="s">
+      <c r="A156" t="s">
         <v>41</v>
       </c>
       <c r="B156">
@@ -8007,7 +8007,7 @@
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A159" s="1" t="s">
+      <c r="A159" t="s">
         <v>41</v>
       </c>
       <c r="B159">
@@ -8054,7 +8054,7 @@
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A160" s="1" t="s">
+      <c r="A160" t="s">
         <v>41</v>
       </c>
       <c r="B160">
